--- a/sampleprojects/TaxReturn/excel/states/CA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/CA.xlsx
@@ -77,7 +77,7 @@
     <t>MFJ/QSS/HOH: $10,726 standard deduction; joint bracket limits</t>
   </si>
   <si>
-    <t>set result.ca_taxable_income = the maximum of (result.agi - ca_standard_deduction_joint) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_joint) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_joint) - ca_bracket_1_limit_joint) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_joint) - ca_bracket_2_limit_joint) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_joint) - ca_bracket_3_limit_joint) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_joint) - ca_bracket_4_limit_joint) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_joint) - ca_bracket_5_limit_joint) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_joint) - ca_bracket_6_limit_joint) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_joint) - ca_bracket_7_limit_joint) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_joint) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
+    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - ca_standard_deduction_joint) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_joint) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_joint) - ca_bracket_1_limit_joint) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_joint) - ca_bracket_2_limit_joint) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_joint) - ca_bracket_3_limit_joint) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_joint) - ca_bracket_4_limit_joint) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_joint) - ca_bracket_5_limit_joint) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_joint) - ca_bracket_6_limit_joint) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_joint) - ca_bracket_7_limit_joint) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_joint) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
   </si>
   <si>
     <t>X</t>
@@ -86,7 +86,7 @@
     <t>Default (Single/MFS): $5,363 standard deduction; single bracket limits</t>
   </si>
   <si>
-    <t>set result.ca_taxable_income = the maximum of (result.agi - ca_standard_deduction_single) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_single) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_single) - ca_bracket_1_limit_single) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_single) - ca_bracket_2_limit_single) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_single) - ca_bracket_3_limit_single) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_single) - ca_bracket_4_limit_single) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_single) - ca_bracket_5_limit_single) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_single) - ca_bracket_6_limit_single) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_single) - ca_bracket_7_limit_single) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_single) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
+    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - ca_standard_deduction_single) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_single) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_single) - ca_bracket_1_limit_single) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_single) - ca_bracket_2_limit_single) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_single) - ca_bracket_3_limit_single) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_single) - ca_bracket_4_limit_single) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_single) - ca_bracket_5_limit_single) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_single) - ca_bracket_6_limit_single) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_single) - ca_bracket_7_limit_single) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_single) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>

--- a/sampleprojects/TaxReturn/excel/states/CA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/CA.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
   <si>
     <t>DT: CA Tax</t>
   </si>
@@ -47,7 +47,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.ca_state_tax = 0.0; set result.ca_taxable_income = 0.0; set result.ca_mhst = 0.0; set result.ca_total_tax = 0.0; add "  California Tax Calculation (Form 540) — 10-bracket progressive 1.0-13.3% + 1% MHST &gt; $1M" to job.audit_trail</t>
+    <t>set result.ca_state_tax = 0.0; set result.ca_taxable_income = 0.0; set result.ca_mhst = 0.0; set result.ca_total_tax = 0.0; add "  California Tax Calculation (Form 540) — 10-bracket progressive 1.0-13.3% + 1% MHST &gt; $1M" to job.audit_trail; set result.ca_military_retirement_exemption = 0.0; perform ca_military_retirement_exemption; add "  CA Schedule CA (540) line 5b column B military retirement exclusion: $" + result.ca_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -77,7 +77,7 @@
     <t>MFJ/QSS/HOH: $10,726 standard deduction; joint bracket limits</t>
   </si>
   <si>
-    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - ca_standard_deduction_joint) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_joint) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_joint) - ca_bracket_1_limit_joint) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_joint) - ca_bracket_2_limit_joint) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_joint) - ca_bracket_3_limit_joint) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_joint) - ca_bracket_4_limit_joint) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_joint) - ca_bracket_5_limit_joint) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_joint) - ca_bracket_6_limit_joint) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_joint) - ca_bracket_7_limit_joint) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_joint) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
+    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - result.ca_military_retirement_exemption - ca_standard_deduction_joint) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_joint) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_joint) - ca_bracket_1_limit_joint) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_joint) - ca_bracket_2_limit_joint) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_joint) - ca_bracket_3_limit_joint) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_joint) - ca_bracket_4_limit_joint) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_joint) - ca_bracket_5_limit_joint) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_joint) - ca_bracket_6_limit_joint) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_joint) - ca_bracket_7_limit_joint) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_joint) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
   </si>
   <si>
     <t>X</t>
@@ -86,7 +86,7 @@
     <t>Default (Single/MFS): $5,363 standard deduction; single bracket limits</t>
   </si>
   <si>
-    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - ca_standard_deduction_single) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_single) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_single) - ca_bracket_1_limit_single) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_single) - ca_bracket_2_limit_single) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_single) - ca_bracket_3_limit_single) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_single) - ca_bracket_4_limit_single) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_single) - ca_bracket_5_limit_single) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_single) - ca_bracket_6_limit_single) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_single) - ca_bracket_7_limit_single) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_single) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
+    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - result.ca_military_retirement_exemption - ca_standard_deduction_single) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_single) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_single) - ca_bracket_1_limit_single) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_single) - ca_bracket_2_limit_single) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_single) - ca_bracket_3_limit_single) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_single) - ca_bracket_4_limit_single) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_single) - ca_bracket_5_limit_single) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_single) - ca_bracket_6_limit_single) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_single) - ca_bracket_7_limit_single) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_single) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>
@@ -125,6 +125,51 @@
     <t>TABLE_NUMBER: 4802</t>
   </si>
   <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has federal retirement pay for uniformed service</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Joint return or surviving spouse: the $250,000 federal AGI limit</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "MFJ" or job.filing_status is equal to "QSS"</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Federal AGI within the joint limit</t>
+  </si>
+  <si>
+    <t>result.state_calc_total_agi &lt;= ca_military_agi_limit_joint</t>
+  </si>
+  <si>
+    <t>Federal AGI within the single limit</t>
+  </si>
+  <si>
+    <t>result.state_calc_total_agi &lt;= ca_military_agi_limit_single</t>
+  </si>
+  <si>
+    <t>Schedule CA (540) Part I Section A line 5b column B: the taxable retirement pay, not to exceed $20,000 (R&amp;TC 17132.9)</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and ca_military_retirement_exemption_amount to result.ca_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Joint return or surviving spouse with federal AGI of $250,000 or less: up to $20,000 of military retirement pay is excluded, Schedule CA (540) line 5b column B (R&amp;TC 17132.9, AB 53; 2025 Schedule CA instructions). Survivor Benefit Plan annuities have their own $20,000 and are not modelled.</t>
+  </si>
+  <si>
+    <t>Any other filer with federal AGI of $125,000 or less: up to $20,000 excluded (R&amp;TC 17132.9).</t>
+  </si>
+  <si>
+    <t>Federal AGI above the limit, or no retirement pay: no exclusion; the limit is a cliff, not a phase-out.</t>
+  </si>
+  <si>
     <t>DT: CA AGI</t>
   </si>
   <si>
@@ -473,7 +518,7 @@
     <t>250000.0</t>
   </si>
   <si>
-    <t>CA AGI limit for military retirement exemption - joint filers (2025)</t>
+    <t>CA military retirement exclusion federal AGI limit, joint return or surviving spouse: $250,000; no exclusion at all above it (2025 Schedule CA (540) instructions, line 5a and 5b).</t>
   </si>
   <si>
     <t>ca_military_agi_limit_single</t>
@@ -482,13 +527,13 @@
     <t>125000.0</t>
   </si>
   <si>
-    <t>CA AGI limit for military retirement exemption - single filers (2025)</t>
+    <t>CA military retirement exclusion federal AGI limit, single, head of household or married filing separately: $125,000; no exclusion at all above it (2025 Schedule CA (540) instructions, line 5a and 5b).</t>
   </si>
   <si>
     <t>ca_military_retirement_exemption</t>
   </si>
   <si>
-    <t>CA military retirement exemption (computed based on AGI and filing status)</t>
+    <t>CA exclusion of military retired pay (computed per taxpayer by ca_military_retirement_exemption): the lesser of the pay and $20,000 when federal AGI is within the filing-status limit, else 0 (#1330).</t>
   </si>
   <si>
     <t>ca_military_retirement_exemption_amount</t>
@@ -497,7 +542,7 @@
     <t>20000.0</t>
   </si>
   <si>
-    <t>CA military retirement exemption amount - $20,000 (2025). Source: MOAA</t>
+    <t>California military retirement exclusion, taxable years 2025-2029: up to $20,000 of federal retirement pay for uniformed service (and separately up to $20,000 of Survivor Benefit Plan annuity), Schedule CA (540) Part I Section A line 5b column B; R&amp;TC 17132.9 and 17132.10 (AB 53, 2025); FTB Pub. 1032.</t>
   </si>
   <si>
     <t>ca_military_retirement_taxable</t>
@@ -2169,157 +2214,715 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E17" s="4">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F17" s="4">
         <v>3</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G17" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H17" s="4">
         <v>5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I17" s="4">
         <v>6</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J17" s="4">
         <v>7</v>
       </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
+      <c r="K17" s="4">
+        <v>8</v>
+      </c>
+      <c r="L17" s="4">
         <v>9</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M17" s="4">
         <v>10</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N17" s="4">
         <v>11</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O17" s="4">
         <v>12</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P17" s="4">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q17" s="4">
         <v>14</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R17" s="4">
         <v>15</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S17" s="4">
         <v>16</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>6</v>
+      </c>
+      <c r="J20" s="1">
+        <v>7</v>
+      </c>
+      <c r="K20" s="1">
+        <v>8</v>
+      </c>
+      <c r="L20" s="1">
+        <v>9</v>
+      </c>
+      <c r="M20" s="1">
+        <v>10</v>
+      </c>
+      <c r="N20" s="1">
+        <v>11</v>
+      </c>
+      <c r="O20" s="1">
+        <v>12</v>
+      </c>
+      <c r="P20" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>14</v>
+      </c>
+      <c r="R20" s="1">
+        <v>15</v>
+      </c>
+      <c r="S20" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2335,7 +2938,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2381,7 +2984,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2404,7 +3007,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2625,56 +3228,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2693,25 +3296,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -2734,25 +3337,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -2775,25 +3378,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -2816,25 +3419,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2857,25 +3460,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -2898,25 +3501,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="H9" s="16" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -2939,25 +3542,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2980,25 +3583,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -3021,25 +3624,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -3062,25 +3665,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -3103,25 +3706,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3144,25 +3747,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3185,25 +3788,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3226,25 +3829,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -3267,25 +3870,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3308,25 +3911,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3349,25 +3952,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -3390,25 +3993,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -3431,25 +4034,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -3472,25 +4075,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -3513,25 +4116,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -3554,25 +4157,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -3595,25 +4198,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -3636,25 +4239,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>8</v>
@@ -3677,25 +4280,25 @@
         <v>8</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>8</v>
@@ -3718,25 +4321,25 @@
         <v>8</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>8</v>
@@ -3759,25 +4362,25 @@
         <v>8</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>8</v>
@@ -3800,25 +4403,25 @@
         <v>8</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>8</v>
@@ -3841,25 +4444,25 @@
         <v>8</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>8</v>
@@ -3882,25 +4485,25 @@
         <v>8</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>8</v>
@@ -3923,25 +4526,25 @@
         <v>8</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>8</v>
@@ -3964,25 +4567,25 @@
         <v>8</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>8</v>
@@ -4005,25 +4608,25 @@
         <v>8</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>8</v>
@@ -4046,25 +4649,25 @@
         <v>8</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>8</v>
@@ -4087,25 +4690,25 @@
         <v>8</v>
       </c>
       <c r="B38" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C38" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>140</v>
-      </c>
       <c r="F38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>8</v>
@@ -4128,25 +4731,25 @@
         <v>8</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>8</v>
@@ -4169,25 +4772,25 @@
         <v>8</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>8</v>
@@ -4210,25 +4813,25 @@
         <v>8</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>8</v>
@@ -4251,25 +4854,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>8</v>
@@ -4292,25 +4895,25 @@
         <v>8</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>8</v>
@@ -4333,25 +4936,25 @@
         <v>8</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>8</v>
@@ -4374,25 +4977,25 @@
         <v>8</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>8</v>
@@ -4415,25 +5018,25 @@
         <v>8</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>8</v>
@@ -4456,25 +5059,25 @@
         <v>8</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>8</v>
@@ -4497,25 +5100,25 @@
         <v>8</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>8</v>
@@ -4538,25 +5141,25 @@
         <v>8</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>8</v>
@@ -4579,25 +5182,25 @@
         <v>8</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>8</v>
@@ -4620,25 +5223,25 @@
         <v>8</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>8</v>
@@ -4661,25 +5264,25 @@
         <v>8</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>8</v>

--- a/sampleprojects/TaxReturn/excel/states/CA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/CA.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t>DT: CA Tax</t>
   </si>
@@ -155,19 +155,25 @@
     <t>result.state_calc_total_agi &lt;= ca_military_agi_limit_single</t>
   </si>
   <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
     <t>Schedule CA (540) Part I Section A line 5b column B: the taxable retirement pay, not to exceed $20,000 (R&amp;TC 17132.9)</t>
   </si>
   <si>
     <t>add the minimum of taxpayer.military_retirement_pay and ca_military_retirement_exemption_amount to result.ca_military_retirement_exemption</t>
   </si>
   <si>
-    <t>Joint return or surviving spouse with federal AGI of $250,000 or less: up to $20,000 of military retirement pay is excluded, Schedule CA (540) line 5b column B (R&amp;TC 17132.9, AB 53; 2025 Schedule CA instructions). Survivor Benefit Plan annuities have their own $20,000 and are not modelled.</t>
+    <t>Joint return or surviving spouse with federal AGI of $250,000 or less: up to $20,000 of military retirement pay is excluded, Schedule CA (540) line 5b column B (R&amp;TC 17132.9; 2025 Schedule CA instructions). Survivor Benefit Plan annuities have their own $20,000 and are not modelled.</t>
   </si>
   <si>
     <t>Any other filer with federal AGI of $125,000 or less: up to $20,000 excluded (R&amp;TC 17132.9).</t>
   </si>
   <si>
-    <t>Federal AGI above the limit, or no retirement pay: no exclusion; the limit is a cliff, not a phase-out.</t>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>DT: CA AGI</t>
@@ -542,7 +548,7 @@
     <t>20000.0</t>
   </si>
   <si>
-    <t>California military retirement exclusion, taxable years 2025-2029: up to $20,000 of federal retirement pay for uniformed service (and separately up to $20,000 of Survivor Benefit Plan annuity), Schedule CA (540) Part I Section A line 5b column B; R&amp;TC 17132.9 and 17132.10 (AB 53, 2025); FTB Pub. 1032.</t>
+    <t>California military retirement exclusion, taxable years 2025-2029: up to $20,000 of federal retirement pay for uniformed service (and separately up to $20,000 of Survivor Benefit Plan annuity), Schedule CA (540) Part I Section A line 5b column B; R&amp;TC 17132.9 and 17132.10; FTB Pub. 1032. The 2025 Schedule CA instructions cite the sections and no bill.</t>
   </si>
   <si>
     <t>ca_military_retirement_taxable</t>
@@ -2343,7 +2349,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -2402,7 +2408,7 @@
         <v>40</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -2461,7 +2467,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -2520,7 +2526,7 @@
         <v>40</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -2559,244 +2565,244 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+    <row r="16">
+      <c r="A16" s="5">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E18" s="4">
         <v>2</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F18" s="4">
         <v>3</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G18" s="4">
         <v>4</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H18" s="4">
         <v>5</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I18" s="4">
         <v>6</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J18" s="4">
         <v>7</v>
       </c>
-      <c r="K17" s="4">
-        <v>8</v>
-      </c>
-      <c r="L17" s="4">
+      <c r="K18" s="4">
+        <v>8</v>
+      </c>
+      <c r="L18" s="4">
         <v>9</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M18" s="4">
         <v>10</v>
       </c>
-      <c r="N17" s="4">
+      <c r="N18" s="4">
         <v>11</v>
       </c>
-      <c r="O17" s="4">
+      <c r="O18" s="4">
         <v>12</v>
       </c>
-      <c r="P17" s="4">
+      <c r="P18" s="4">
         <v>13</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="Q18" s="4">
         <v>14</v>
       </c>
-      <c r="R17" s="4">
+      <c r="R18" s="4">
         <v>15</v>
       </c>
-      <c r="S17" s="4">
+      <c r="S18" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5">
+    <row r="19">
+      <c r="A19" s="5">
         <v>1</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>1</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F21" s="1">
         <v>3</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G21" s="1">
         <v>4</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H21" s="1">
         <v>5</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I21" s="1">
         <v>6</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J21" s="1">
         <v>7</v>
       </c>
-      <c r="K20" s="1">
-        <v>8</v>
-      </c>
-      <c r="L20" s="1">
+      <c r="K21" s="1">
+        <v>8</v>
+      </c>
+      <c r="L21" s="1">
         <v>9</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M21" s="1">
         <v>10</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N21" s="1">
         <v>11</v>
       </c>
-      <c r="O20" s="1">
+      <c r="O21" s="1">
         <v>12</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P21" s="1">
         <v>13</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q21" s="1">
         <v>14</v>
       </c>
-      <c r="R20" s="1">
+      <c r="R21" s="1">
         <v>15</v>
       </c>
-      <c r="S20" s="1">
+      <c r="S21" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5">
-        <v>1</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>8</v>
@@ -2852,60 +2858,119 @@
     </row>
     <row r="23">
       <c r="A23" s="5">
+        <v>2</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
         <v>3</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S23" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2921,8 +2986,8 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2938,7 +3003,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2984,7 +3049,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3007,7 +3072,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3228,56 +3293,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -3296,25 +3361,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -3337,25 +3402,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="H5" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -3378,25 +3443,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -3419,25 +3484,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -3460,25 +3525,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -3501,25 +3566,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -3542,25 +3607,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -3583,25 +3648,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -3624,25 +3689,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -3665,25 +3730,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -3706,25 +3771,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3747,25 +3812,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3788,25 +3853,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3829,25 +3894,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -3870,25 +3935,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3911,25 +3976,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3952,25 +4017,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -3993,25 +4058,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -4034,25 +4099,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -4075,25 +4140,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -4116,25 +4181,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -4157,25 +4222,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -4198,25 +4263,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -4239,25 +4304,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>8</v>
@@ -4280,25 +4345,25 @@
         <v>8</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>8</v>
@@ -4321,25 +4386,25 @@
         <v>8</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>8</v>
@@ -4362,25 +4427,25 @@
         <v>8</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>147</v>
-      </c>
       <c r="F30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>8</v>
@@ -4403,25 +4468,25 @@
         <v>8</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>8</v>
@@ -4444,25 +4509,25 @@
         <v>8</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>8</v>
@@ -4485,25 +4550,25 @@
         <v>8</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>8</v>
@@ -4526,25 +4591,25 @@
         <v>8</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>8</v>
@@ -4567,25 +4632,25 @@
         <v>8</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>8</v>
@@ -4608,25 +4673,25 @@
         <v>8</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>8</v>
@@ -4649,25 +4714,25 @@
         <v>8</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>8</v>
@@ -4690,25 +4755,25 @@
         <v>8</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>8</v>
@@ -4731,25 +4796,25 @@
         <v>8</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>8</v>
@@ -4772,25 +4837,25 @@
         <v>8</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>8</v>
@@ -4813,25 +4878,25 @@
         <v>8</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>8</v>
@@ -4854,25 +4919,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>8</v>
@@ -4895,25 +4960,25 @@
         <v>8</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>8</v>
@@ -4936,25 +5001,25 @@
         <v>8</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>8</v>
@@ -4977,25 +5042,25 @@
         <v>8</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>8</v>
@@ -5018,25 +5083,25 @@
         <v>8</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>8</v>
@@ -5059,25 +5124,25 @@
         <v>8</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>8</v>
@@ -5100,25 +5165,25 @@
         <v>8</v>
       </c>
       <c r="B48" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>195</v>
-      </c>
       <c r="F48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>8</v>
@@ -5141,25 +5206,25 @@
         <v>8</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>8</v>
@@ -5182,25 +5247,25 @@
         <v>8</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>8</v>
@@ -5223,25 +5288,25 @@
         <v>8</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>8</v>
@@ -5264,25 +5329,25 @@
         <v>8</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>8</v>

--- a/sampleprojects/TaxReturn/excel/states/CA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/CA.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t>DT: CA Tax</t>
   </si>
@@ -47,7 +47,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.ca_state_tax = 0.0; set result.ca_taxable_income = 0.0; set result.ca_mhst = 0.0; set result.ca_total_tax = 0.0; add "  California Tax Calculation (Form 540) — 10-bracket progressive 1.0-13.3% + 1% MHST &gt; $1M" to job.audit_trail</t>
+    <t>set result.ca_state_tax = 0.0; set result.ca_taxable_income = 0.0; set result.ca_mhst = 0.0; set result.ca_total_tax = 0.0; add "  California Tax Calculation (Form 540) — 10-bracket progressive 1.0-13.3% + 1% MHST &gt; $1M" to job.audit_trail; set result.ca_military_retirement_exemption = 0.0; perform ca_military_retirement_exemption; add "  CA Schedule CA (540) line 5b column B military retirement exclusion: $" + result.ca_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -77,7 +77,7 @@
     <t>MFJ/QSS/HOH: $10,726 standard deduction; joint bracket limits</t>
   </si>
   <si>
-    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - ca_standard_deduction_joint) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_joint) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_joint) - ca_bracket_1_limit_joint) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_joint) - ca_bracket_2_limit_joint) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_joint) - ca_bracket_3_limit_joint) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_joint) - ca_bracket_4_limit_joint) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_joint) - ca_bracket_5_limit_joint) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_joint) - ca_bracket_6_limit_joint) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_joint) - ca_bracket_7_limit_joint) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_joint) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
+    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - result.ca_military_retirement_exemption - ca_standard_deduction_joint) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_joint) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_joint) - ca_bracket_1_limit_joint) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_joint) - ca_bracket_2_limit_joint) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_joint) - ca_bracket_3_limit_joint) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_joint) - ca_bracket_4_limit_joint) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_joint) - ca_bracket_5_limit_joint) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_joint) - ca_bracket_6_limit_joint) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_joint) - ca_bracket_7_limit_joint) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_joint) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
   </si>
   <si>
     <t>X</t>
@@ -86,7 +86,7 @@
     <t>Default (Single/MFS): $5,363 standard deduction; single bracket limits</t>
   </si>
   <si>
-    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - ca_standard_deduction_single) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_single) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_single) - ca_bracket_1_limit_single) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_single) - ca_bracket_2_limit_single) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_single) - ca_bracket_3_limit_single) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_single) - ca_bracket_4_limit_single) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_single) - ca_bracket_5_limit_single) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_single) - ca_bracket_6_limit_single) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_single) - ca_bracket_7_limit_single) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_single) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
+    <t>set result.ca_taxable_income = the maximum of (result.state_calc_agi - result.ca_military_retirement_exemption - ca_standard_deduction_single) and 0.0; set result.ca_state_tax = the maximum of (the minimum of result.ca_taxable_income and ca_bracket_1_limit_single) and 0.0 * ca_bracket_1_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_2_limit_single) - ca_bracket_1_limit_single) and 0.0 * ca_bracket_2_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_3_limit_single) - ca_bracket_2_limit_single) and 0.0 * ca_bracket_3_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_4_limit_single) - ca_bracket_3_limit_single) and 0.0 * ca_bracket_4_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_5_limit_single) - ca_bracket_4_limit_single) and 0.0 * ca_bracket_5_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_6_limit_single) - ca_bracket_5_limit_single) and 0.0 * ca_bracket_6_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_7_limit_single) - ca_bracket_6_limit_single) and 0.0 * ca_bracket_7_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of ((the minimum of result.ca_taxable_income and ca_bracket_8_limit_single) - ca_bracket_7_limit_single) and 0.0 * ca_bracket_8_rate; set result.ca_state_tax = result.ca_state_tax + the maximum of (result.ca_taxable_income - ca_bracket_8_limit_single) and 0.0 * ca_bracket_9_rate; set result.ca_mhst = the maximum of (result.ca_taxable_income - ca_mental_health_tax_threshold) and 0.0 * ca_mental_health_tax_rate; set result.ca_state_tax = result.ca_state_tax + result.ca_mhst; set result.ca_total_tax = result.ca_state_tax</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>
@@ -125,6 +125,57 @@
     <t>TABLE_NUMBER: 4802</t>
   </si>
   <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has federal retirement pay for uniformed service</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Joint return or surviving spouse: the $250,000 federal AGI limit</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "MFJ" or job.filing_status is equal to "QSS"</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Federal AGI within the joint limit</t>
+  </si>
+  <si>
+    <t>result.state_calc_total_agi &lt;= ca_military_agi_limit_joint</t>
+  </si>
+  <si>
+    <t>Federal AGI within the single limit</t>
+  </si>
+  <si>
+    <t>result.state_calc_total_agi &lt;= ca_military_agi_limit_single</t>
+  </si>
+  <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>Schedule CA (540) Part I Section A line 5b column B: the taxable retirement pay, not to exceed $20,000 (R&amp;TC 17132.9)</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and ca_military_retirement_exemption_amount to result.ca_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Joint return or surviving spouse with federal AGI of $250,000 or less: up to $20,000 of military retirement pay is excluded, Schedule CA (540) line 5b column B (R&amp;TC 17132.9; 2025 Schedule CA instructions). Survivor Benefit Plan annuities have their own $20,000 and are not modelled.</t>
+  </si>
+  <si>
+    <t>Any other filer with federal AGI of $125,000 or less: up to $20,000 excluded (R&amp;TC 17132.9).</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
+  </si>
+  <si>
     <t>DT: CA AGI</t>
   </si>
   <si>
@@ -473,7 +524,7 @@
     <t>250000.0</t>
   </si>
   <si>
-    <t>CA AGI limit for military retirement exemption - joint filers (2025)</t>
+    <t>CA military retirement exclusion federal AGI limit, joint return or surviving spouse: $250,000; no exclusion at all above it (2025 Schedule CA (540) instructions, line 5a and 5b).</t>
   </si>
   <si>
     <t>ca_military_agi_limit_single</t>
@@ -482,13 +533,13 @@
     <t>125000.0</t>
   </si>
   <si>
-    <t>CA AGI limit for military retirement exemption - single filers (2025)</t>
+    <t>CA military retirement exclusion federal AGI limit, single, head of household or married filing separately: $125,000; no exclusion at all above it (2025 Schedule CA (540) instructions, line 5a and 5b).</t>
   </si>
   <si>
     <t>ca_military_retirement_exemption</t>
   </si>
   <si>
-    <t>CA military retirement exemption (computed based on AGI and filing status)</t>
+    <t>CA exclusion of military retired pay (computed per taxpayer by ca_military_retirement_exemption): the lesser of the pay and $20,000 when federal AGI is within the filing-status limit, else 0 (#1330).</t>
   </si>
   <si>
     <t>ca_military_retirement_exemption_amount</t>
@@ -497,7 +548,7 @@
     <t>20000.0</t>
   </si>
   <si>
-    <t>CA military retirement exemption amount - $20,000 (2025). Source: MOAA</t>
+    <t>California military retirement exclusion, taxable years 2025-2029: up to $20,000 of federal retirement pay for uniformed service (and separately up to $20,000 of Survivor Benefit Plan annuity), Schedule CA (540) Part I Section A line 5b column B; R&amp;TC 17132.9 and 17132.10; FTB Pub. 1032. The 2025 Schedule CA instructions cite the sections and no bill.</t>
   </si>
   <si>
     <t>ca_military_retirement_taxable</t>
@@ -2169,157 +2220,774 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E18" s="4">
         <v>2</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F18" s="4">
         <v>3</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G18" s="4">
         <v>4</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H18" s="4">
         <v>5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I18" s="4">
         <v>6</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J18" s="4">
         <v>7</v>
       </c>
-      <c r="K12" s="4">
-        <v>8</v>
-      </c>
-      <c r="L12" s="4">
+      <c r="K18" s="4">
+        <v>8</v>
+      </c>
+      <c r="L18" s="4">
         <v>9</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M18" s="4">
         <v>10</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N18" s="4">
         <v>11</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O18" s="4">
         <v>12</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P18" s="4">
         <v>13</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q18" s="4">
         <v>14</v>
       </c>
-      <c r="R12" s="4">
+      <c r="R18" s="4">
         <v>15</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S18" s="4">
         <v>16</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>6</v>
+      </c>
+      <c r="J21" s="1">
+        <v>7</v>
+      </c>
+      <c r="K21" s="1">
+        <v>8</v>
+      </c>
+      <c r="L21" s="1">
+        <v>9</v>
+      </c>
+      <c r="M21" s="1">
+        <v>10</v>
+      </c>
+      <c r="N21" s="1">
+        <v>11</v>
+      </c>
+      <c r="O21" s="1">
+        <v>12</v>
+      </c>
+      <c r="P21" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>14</v>
+      </c>
+      <c r="R21" s="1">
+        <v>15</v>
+      </c>
+      <c r="S21" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <v>2</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
     <mergeCell ref="A4:S4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:S6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2335,7 +3003,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2381,7 +3049,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2404,7 +3072,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2625,56 +3293,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2693,25 +3361,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -2734,25 +3402,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -2775,25 +3443,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -2816,25 +3484,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2857,25 +3525,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -2898,25 +3566,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -2939,25 +3607,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="H10" s="16" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -2980,25 +3648,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -3021,25 +3689,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -3062,25 +3730,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -3103,25 +3771,25 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3144,25 +3812,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3185,25 +3853,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3226,25 +3894,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -3267,25 +3935,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3308,25 +3976,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3349,25 +4017,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -3390,25 +4058,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -3431,25 +4099,25 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -3472,25 +4140,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -3513,25 +4181,25 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -3554,25 +4222,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -3595,25 +4263,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -3636,25 +4304,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>8</v>
@@ -3677,25 +4345,25 @@
         <v>8</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>8</v>
@@ -3718,25 +4386,25 @@
         <v>8</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>8</v>
@@ -3759,25 +4427,25 @@
         <v>8</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>8</v>
@@ -3800,25 +4468,25 @@
         <v>8</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>8</v>
@@ -3841,25 +4509,25 @@
         <v>8</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>8</v>
@@ -3882,25 +4550,25 @@
         <v>8</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>8</v>
@@ -3923,25 +4591,25 @@
         <v>8</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>8</v>
@@ -3964,25 +4632,25 @@
         <v>8</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>8</v>
@@ -4005,25 +4673,25 @@
         <v>8</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>8</v>
@@ -4046,25 +4714,25 @@
         <v>8</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>8</v>
@@ -4087,25 +4755,25 @@
         <v>8</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>8</v>
@@ -4128,25 +4796,25 @@
         <v>8</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>8</v>
@@ -4169,25 +4837,25 @@
         <v>8</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>8</v>
@@ -4210,25 +4878,25 @@
         <v>8</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>8</v>
@@ -4251,25 +4919,25 @@
         <v>8</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>8</v>
@@ -4292,25 +4960,25 @@
         <v>8</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>8</v>
@@ -4333,25 +5001,25 @@
         <v>8</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>8</v>
@@ -4374,25 +5042,25 @@
         <v>8</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>8</v>
@@ -4415,25 +5083,25 @@
         <v>8</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>8</v>
@@ -4456,25 +5124,25 @@
         <v>8</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>8</v>
@@ -4497,25 +5165,25 @@
         <v>8</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>8</v>
@@ -4538,25 +5206,25 @@
         <v>8</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>8</v>
@@ -4579,25 +5247,25 @@
         <v>8</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>8</v>
@@ -4620,25 +5288,25 @@
         <v>8</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>8</v>
@@ -4661,25 +5329,25 @@
         <v>8</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>8</v>
